--- a/MRK GR.xlsx
+++ b/MRK GR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{882A44A9-5631-44EE-AEBA-A4A34518648E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA0812A5-1E76-4C64-AE68-EFBC9FB4E870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20210" yWindow="1180" windowWidth="16190" windowHeight="18170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11100" yWindow="4400" windowWidth="19050" windowHeight="16100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="7" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="176">
   <si>
     <t>Euthyrox</t>
   </si>
@@ -594,6 +594,9 @@
   </si>
   <si>
     <t>Q425</t>
+  </si>
+  <si>
+    <t>Q126</t>
   </si>
 </sst>
 </file>
@@ -1452,7 +1455,7 @@
         <v>10</v>
       </c>
       <c r="J2" s="11">
-        <v>171.8</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="2:12">
@@ -1498,7 +1501,7 @@
       </c>
       <c r="J4" s="12">
         <f>J3*J2</f>
-        <v>74694.839440399999</v>
+        <v>60434.125042</v>
       </c>
       <c r="K4" s="13"/>
     </row>
@@ -1522,7 +1525,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="26" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" spans="2:12">
@@ -1538,10 +1541,10 @@
         <v>12</v>
       </c>
       <c r="J6" s="12">
-        <v>7121.1</v>
+        <v>8318</v>
       </c>
       <c r="K6" s="26" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="2:12">
@@ -1560,7 +1563,7 @@
       </c>
       <c r="J7" s="12">
         <f>J4-J5+J6</f>
-        <v>81815.939440400005</v>
+        <v>68752.125042</v>
       </c>
     </row>
     <row r="8" spans="2:12" ht="13">
@@ -3926,39 +3929,39 @@
         <v>5754</v>
       </c>
       <c r="CB17" s="22">
-        <f>SUM(K17:N17)</f>
+        <f t="shared" ref="CB17:CJ17" si="27">SUM(K17:N17)</f>
         <v>5762.5999999999995</v>
       </c>
       <c r="CC17" s="22">
-        <f>SUM(L17:O17)</f>
+        <f t="shared" si="27"/>
         <v>4417.7</v>
       </c>
       <c r="CD17" s="22">
-        <f>SUM(M17:P17)</f>
+        <f t="shared" si="27"/>
         <v>2967.2</v>
       </c>
       <c r="CE17" s="22">
-        <f>SUM(N17:Q17)</f>
+        <f t="shared" si="27"/>
         <v>1573.7</v>
       </c>
       <c r="CF17" s="22">
-        <f>SUM(O17:R17)</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="CG17" s="22">
-        <f>SUM(P17:S17)</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="CH17" s="22">
-        <f>SUM(Q17:T17)</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="CI17" s="22">
-        <f>SUM(R17:U17)</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="CJ17" s="22">
-        <f>SUM(S17:V17)</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="CK17" s="22">
@@ -3986,23 +3989,23 @@
         <v>0</v>
       </c>
       <c r="CQ17" s="22">
-        <f t="shared" ref="CQ17" si="27">SUM(Z17:AC17)</f>
+        <f t="shared" ref="CQ17" si="28">SUM(Z17:AC17)</f>
         <v>0</v>
       </c>
       <c r="CR17" s="22">
-        <f t="shared" ref="CR17" si="28">SUM(AA17:AD17)</f>
+        <f t="shared" ref="CR17" si="29">SUM(AA17:AD17)</f>
         <v>0</v>
       </c>
       <c r="CS17" s="22">
-        <f t="shared" ref="CS17" si="29">SUM(AB17:AE17)</f>
+        <f t="shared" ref="CS17" si="30">SUM(AB17:AE17)</f>
         <v>0</v>
       </c>
       <c r="CT17" s="22">
-        <f t="shared" ref="CT17" si="30">SUM(AC17:AF17)</f>
+        <f t="shared" ref="CT17" si="31">SUM(AC17:AF17)</f>
         <v>0</v>
       </c>
       <c r="CU17" s="22">
-        <f t="shared" ref="CU17" si="31">SUM(AD17:AG17)</f>
+        <f t="shared" ref="CU17" si="32">SUM(AD17:AG17)</f>
         <v>0</v>
       </c>
     </row>
@@ -4037,11 +4040,11 @@
         <v>119.59500000000001</v>
       </c>
       <c r="M18" s="18">
-        <f t="shared" ref="M18:N18" si="32">+I18*1.05</f>
+        <f t="shared" ref="M18:N18" si="33">+I18*1.05</f>
         <v>131.25</v>
       </c>
       <c r="N18" s="18">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>132.51</v>
       </c>
       <c r="O18" s="18"/>
@@ -4108,11 +4111,11 @@
       <c r="BY18" s="18"/>
       <c r="BZ18" s="18"/>
       <c r="CA18" s="18">
-        <f t="shared" ref="CA18:CA45" si="33">SUM(G18:J18)</f>
+        <f t="shared" ref="CA18:CA45" si="34">SUM(G18:J18)</f>
         <v>472</v>
       </c>
       <c r="CB18" s="18">
-        <f t="shared" ref="CB18:CB30" si="34">SUM(K18:N18)</f>
+        <f t="shared" ref="CB18:CB30" si="35">SUM(K18:N18)</f>
         <v>499.55500000000001</v>
       </c>
       <c r="CC18" s="18"/>
@@ -4480,23 +4483,23 @@
         <v>244.4</v>
       </c>
       <c r="BF22" s="18">
-        <f t="shared" ref="BF22:BJ22" si="35">+BE22</f>
+        <f t="shared" ref="BF22:BJ22" si="36">+BE22</f>
         <v>244.4</v>
       </c>
       <c r="BG22" s="18">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>244.4</v>
       </c>
       <c r="BH22" s="18">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>244.4</v>
       </c>
       <c r="BI22" s="18">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>244.4</v>
       </c>
       <c r="BJ22" s="18">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>244.4</v>
       </c>
       <c r="BK22" s="18"/>
@@ -4586,23 +4589,23 @@
         <v>1246.4000000000001</v>
       </c>
       <c r="BF23" s="18">
-        <f t="shared" ref="BF23:BJ23" si="36">+BE23</f>
+        <f t="shared" ref="BF23:BJ23" si="37">+BE23</f>
         <v>1246.4000000000001</v>
       </c>
       <c r="BG23" s="18">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1246.4000000000001</v>
       </c>
       <c r="BH23" s="18">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1246.4000000000001</v>
       </c>
       <c r="BI23" s="18">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1246.4000000000001</v>
       </c>
       <c r="BJ23" s="18">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1246.4000000000001</v>
       </c>
       <c r="BK23" s="18"/>
@@ -4705,23 +4708,23 @@
         <v>1190</v>
       </c>
       <c r="BF24" s="18">
-        <f t="shared" ref="BF24:BJ24" si="37">+BB24*1.05</f>
+        <f t="shared" ref="BF24:BJ24" si="38">+BB24*1.05</f>
         <v>1324.05</v>
       </c>
       <c r="BG24" s="18">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1313.865</v>
       </c>
       <c r="BH24" s="18">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1206.45</v>
       </c>
       <c r="BI24" s="18">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1249.5</v>
       </c>
       <c r="BJ24" s="18">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1390.2525000000001</v>
       </c>
       <c r="BK24" s="18"/>
@@ -4782,11 +4785,11 @@
         <v>613.4</v>
       </c>
       <c r="M25" s="22">
-        <f t="shared" ref="M25:N25" si="38">+L25+5</f>
+        <f t="shared" ref="M25:N25" si="39">+L25+5</f>
         <v>618.4</v>
       </c>
       <c r="N25" s="22">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>623.4</v>
       </c>
       <c r="O25" s="22"/>
@@ -4818,35 +4821,35 @@
       <c r="AO25" s="22"/>
       <c r="AP25" s="22"/>
       <c r="AQ25" s="22">
-        <f t="shared" ref="AQ25:AX25" si="39">SUM(AQ20:AQ24)</f>
+        <f t="shared" ref="AQ25:AX25" si="40">SUM(AQ20:AQ24)</f>
         <v>0</v>
       </c>
       <c r="AR25" s="22">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AS25" s="22">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AT25" s="22">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AU25" s="22">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AV25" s="22">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1806</v>
       </c>
       <c r="AW25" s="22">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1910</v>
       </c>
       <c r="AX25" s="22">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AY25" s="22">
@@ -4870,31 +4873,31 @@
         <v>2445.3000000000002</v>
       </c>
       <c r="BD25" s="22">
-        <f t="shared" ref="BD25:BJ25" si="40">SUM(BD20:BD24)</f>
+        <f t="shared" ref="BD25:BJ25" si="41">SUM(BD20:BD24)</f>
         <v>2648</v>
       </c>
       <c r="BE25" s="22">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>2680.8</v>
       </c>
       <c r="BF25" s="22">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>2814.8500000000004</v>
       </c>
       <c r="BG25" s="22">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>2804.665</v>
       </c>
       <c r="BH25" s="22">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>2697.25</v>
       </c>
       <c r="BI25" s="22">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>2740.3</v>
       </c>
       <c r="BJ25" s="22">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>2881.0525000000002</v>
       </c>
       <c r="BK25" s="22">
@@ -4923,43 +4926,43 @@
       <c r="BY25" s="22"/>
       <c r="BZ25" s="22"/>
       <c r="CA25" s="22">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>1680.9999999999998</v>
       </c>
       <c r="CB25" s="22">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>2463.6</v>
       </c>
       <c r="CC25" s="22">
-        <f t="shared" ref="CC25:CU25" si="41">SUM(CC20:CC24)</f>
+        <f t="shared" ref="CC25:CU25" si="42">SUM(CC20:CC24)</f>
         <v>0</v>
       </c>
       <c r="CD25" s="22">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="CE25" s="22">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="CF25" s="22">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="CG25" s="22">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="CH25" s="22">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="CI25" s="22">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="CJ25" s="22">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="CK25" s="22">
@@ -4971,39 +4974,39 @@
         <v>8990</v>
       </c>
       <c r="CM25" s="22">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="CN25" s="22">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="CO25" s="22">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="CP25" s="22">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="CQ25" s="22">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="CR25" s="22">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="CS25" s="22">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="CT25" s="22">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="CU25" s="22">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
     </row>
@@ -5167,23 +5170,23 @@
         <v>106.4</v>
       </c>
       <c r="BF27" s="18">
-        <f t="shared" ref="BF27:BF28" si="42">+BB27*1.1</f>
+        <f t="shared" ref="BF27:BF28" si="43">+BB27*1.1</f>
         <v>108.9</v>
       </c>
       <c r="BG27" s="18">
-        <f t="shared" ref="BG27:BG28" si="43">+BC27*1.1</f>
+        <f t="shared" ref="BG27:BG28" si="44">+BC27*1.1</f>
         <v>126.50000000000001</v>
       </c>
       <c r="BH27" s="18">
-        <f t="shared" ref="BH27:BH28" si="44">+BD27*1.1</f>
+        <f t="shared" ref="BH27:BH28" si="45">+BD27*1.1</f>
         <v>122.10000000000001</v>
       </c>
       <c r="BI27" s="18">
-        <f t="shared" ref="BI27:BI28" si="45">+BE27*1.1</f>
+        <f t="shared" ref="BI27:BI28" si="46">+BE27*1.1</f>
         <v>117.04000000000002</v>
       </c>
       <c r="BJ27" s="18">
-        <f t="shared" ref="BJ27:BJ28" si="46">+BF27*1.1</f>
+        <f t="shared" ref="BJ27:BJ28" si="47">+BF27*1.1</f>
         <v>119.79000000000002</v>
       </c>
       <c r="BK27" s="18"/>
@@ -5290,23 +5293,23 @@
         <v>200.4</v>
       </c>
       <c r="BF28" s="18">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>277.20000000000005</v>
       </c>
       <c r="BG28" s="18">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>288.20000000000005</v>
       </c>
       <c r="BH28" s="18">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>256.3</v>
       </c>
       <c r="BI28" s="18">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>220.44000000000003</v>
       </c>
       <c r="BJ28" s="18">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>304.92000000000007</v>
       </c>
       <c r="BK28" s="18"/>
@@ -5413,23 +5416,23 @@
         <v>729</v>
       </c>
       <c r="BF29" s="18">
-        <f t="shared" ref="BF29:BJ29" si="47">+BB29*1.3</f>
+        <f t="shared" ref="BF29:BJ29" si="48">+BB29*1.3</f>
         <v>783.9</v>
       </c>
       <c r="BG29" s="18">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>755.30000000000007</v>
       </c>
       <c r="BH29" s="18">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>848.9</v>
       </c>
       <c r="BI29" s="18">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>947.7</v>
       </c>
       <c r="BJ29" s="18">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>1019.07</v>
       </c>
       <c r="BK29" s="18"/>
@@ -5490,11 +5493,11 @@
         <v>395.89</v>
       </c>
       <c r="M30" s="22">
-        <f t="shared" ref="M30:N30" si="48">+I30*1.1</f>
+        <f t="shared" ref="M30:N30" si="49">+I30*1.1</f>
         <v>380.27000000000004</v>
       </c>
       <c r="N30" s="22">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>359.70000000000005</v>
       </c>
       <c r="O30" s="22"/>
@@ -5526,35 +5529,35 @@
       <c r="AO30" s="22"/>
       <c r="AP30" s="22"/>
       <c r="AQ30" s="22">
-        <f t="shared" ref="AQ30:AX30" si="49">SUM(AQ27:AQ29)</f>
+        <f t="shared" ref="AQ30:AX30" si="50">SUM(AQ27:AQ29)</f>
         <v>0</v>
       </c>
       <c r="AR30" s="22">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="AS30" s="22">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="AT30" s="22">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="AU30" s="22">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="AV30" s="22">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="AW30" s="22">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>835</v>
       </c>
       <c r="AX30" s="22">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="AY30" s="22">
@@ -5581,27 +5584,27 @@
         <v>997</v>
       </c>
       <c r="BE30" s="22">
-        <f t="shared" ref="BE30:BJ30" si="50">SUM(BE27:BE29)</f>
+        <f t="shared" ref="BE30:BJ30" si="51">SUM(BE27:BE29)</f>
         <v>1035.8</v>
       </c>
       <c r="BF30" s="22">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1170</v>
       </c>
       <c r="BG30" s="22">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1170</v>
       </c>
       <c r="BH30" s="22">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1227.3</v>
       </c>
       <c r="BI30" s="22">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1285.18</v>
       </c>
       <c r="BJ30" s="22">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1443.7800000000002</v>
       </c>
       <c r="BK30" s="22">
@@ -5630,87 +5633,87 @@
       <c r="BY30" s="22"/>
       <c r="BZ30" s="22"/>
       <c r="CA30" s="22">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>1384</v>
       </c>
       <c r="CB30" s="22">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>1543.8600000000001</v>
       </c>
       <c r="CC30" s="22">
-        <f t="shared" ref="CC30" si="51">SUM(CC27:CC29)</f>
+        <f t="shared" ref="CC30" si="52">SUM(CC27:CC29)</f>
         <v>0</v>
       </c>
       <c r="CD30" s="22">
-        <f t="shared" ref="CD30" si="52">SUM(CD27:CD29)</f>
+        <f t="shared" ref="CD30" si="53">SUM(CD27:CD29)</f>
         <v>0</v>
       </c>
       <c r="CE30" s="22">
-        <f t="shared" ref="CE30" si="53">SUM(CE27:CE29)</f>
+        <f t="shared" ref="CE30" si="54">SUM(CE27:CE29)</f>
         <v>0</v>
       </c>
       <c r="CF30" s="22">
-        <f t="shared" ref="CF30" si="54">SUM(CF27:CF29)</f>
+        <f t="shared" ref="CF30" si="55">SUM(CF27:CF29)</f>
         <v>0</v>
       </c>
       <c r="CG30" s="22">
-        <f t="shared" ref="CG30" si="55">SUM(CG27:CG29)</f>
+        <f t="shared" ref="CG30" si="56">SUM(CG27:CG29)</f>
         <v>0</v>
       </c>
       <c r="CH30" s="22">
-        <f t="shared" ref="CH30" si="56">SUM(CH27:CH29)</f>
+        <f t="shared" ref="CH30" si="57">SUM(CH27:CH29)</f>
         <v>0</v>
       </c>
       <c r="CI30" s="22">
-        <f t="shared" ref="CI30" si="57">SUM(CI27:CI29)</f>
+        <f t="shared" ref="CI30" si="58">SUM(CI27:CI29)</f>
         <v>0</v>
       </c>
       <c r="CJ30" s="22">
-        <f t="shared" ref="CJ30" si="58">SUM(CJ27:CJ29)</f>
+        <f t="shared" ref="CJ30" si="59">SUM(CJ27:CJ29)</f>
         <v>0</v>
       </c>
       <c r="CK30" s="22">
-        <f t="shared" ref="CK30" si="59">SUM(CK27:CK29)</f>
+        <f t="shared" ref="CK30" si="60">SUM(CK27:CK29)</f>
         <v>3380</v>
       </c>
       <c r="CL30" s="22">
-        <f t="shared" ref="CL30" si="60">SUM(CL27:CL29)</f>
+        <f t="shared" ref="CL30" si="61">SUM(CL27:CL29)</f>
         <v>3607</v>
       </c>
       <c r="CM30" s="22">
-        <f t="shared" ref="CM30" si="61">SUM(CM27:CM29)</f>
+        <f t="shared" ref="CM30" si="62">SUM(CM27:CM29)</f>
         <v>0</v>
       </c>
       <c r="CN30" s="22">
-        <f t="shared" ref="CN30" si="62">SUM(CN27:CN29)</f>
+        <f t="shared" ref="CN30" si="63">SUM(CN27:CN29)</f>
         <v>0</v>
       </c>
       <c r="CO30" s="22">
-        <f t="shared" ref="CO30" si="63">SUM(CO27:CO29)</f>
+        <f t="shared" ref="CO30" si="64">SUM(CO27:CO29)</f>
         <v>0</v>
       </c>
       <c r="CP30" s="22">
-        <f t="shared" ref="CP30" si="64">SUM(CP27:CP29)</f>
+        <f t="shared" ref="CP30" si="65">SUM(CP27:CP29)</f>
         <v>0</v>
       </c>
       <c r="CQ30" s="22">
-        <f t="shared" ref="CQ30" si="65">SUM(CQ27:CQ29)</f>
+        <f t="shared" ref="CQ30" si="66">SUM(CQ27:CQ29)</f>
         <v>0</v>
       </c>
       <c r="CR30" s="22">
-        <f t="shared" ref="CR30" si="66">SUM(CR27:CR29)</f>
+        <f t="shared" ref="CR30" si="67">SUM(CR27:CR29)</f>
         <v>0</v>
       </c>
       <c r="CS30" s="22">
-        <f t="shared" ref="CS30" si="67">SUM(CS27:CS29)</f>
+        <f t="shared" ref="CS30" si="68">SUM(CS27:CS29)</f>
         <v>0</v>
       </c>
       <c r="CT30" s="22">
-        <f t="shared" ref="CT30" si="68">SUM(CT27:CT29)</f>
+        <f t="shared" ref="CT30" si="69">SUM(CT27:CT29)</f>
         <v>0</v>
       </c>
       <c r="CU30" s="22">
-        <f t="shared" ref="CU30" si="69">SUM(CU27:CU29)</f>
+        <f t="shared" ref="CU30" si="70">SUM(CU27:CU29)</f>
         <v>0</v>
       </c>
     </row>
@@ -5880,7 +5883,7 @@
       <c r="BY32" s="18"/>
       <c r="BZ32" s="18"/>
       <c r="CA32" s="18">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>76.099999999999994</v>
       </c>
       <c r="CB32" s="18">
@@ -5923,15 +5926,15 @@
         <v>2563.6999999999998</v>
       </c>
       <c r="L33" s="22">
-        <f t="shared" ref="L33:N33" si="70">SUM(L17:L32)</f>
+        <f t="shared" ref="L33:N33" si="71">SUM(L17:L32)</f>
         <v>2579.3849999999998</v>
       </c>
       <c r="M33" s="22">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>2523.42</v>
       </c>
       <c r="N33" s="22">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>2689.3100000000004</v>
       </c>
       <c r="O33" s="22"/>
@@ -5987,83 +5990,83 @@
         <v>4598.5</v>
       </c>
       <c r="AY33" s="22">
-        <f t="shared" ref="AY33:BD33" si="71">AY30+AY25+AY17</f>
+        <f t="shared" ref="AY33:BD33" si="72">AY30+AY25+AY17</f>
         <v>4630</v>
       </c>
       <c r="AZ33" s="22">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>4871</v>
       </c>
       <c r="BA33" s="22">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>4971</v>
       </c>
       <c r="BB33" s="22">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>5214</v>
       </c>
       <c r="BC33" s="22">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>5198.3</v>
       </c>
       <c r="BD33" s="22">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>5569</v>
       </c>
       <c r="BE33" s="22">
-        <f t="shared" ref="BE33:BR33" si="72">BE30+BE25+BE17</f>
+        <f t="shared" ref="BE33:BR33" si="73">BE30+BE25+BE17</f>
         <v>5805.6</v>
       </c>
       <c r="BF33" s="22">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>5823.2000000000007</v>
       </c>
       <c r="BG33" s="22">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>5741.2649999999994</v>
       </c>
       <c r="BH33" s="22">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>5823.5</v>
       </c>
       <c r="BI33" s="22">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>6087.18</v>
       </c>
       <c r="BJ33" s="22">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>6147.63</v>
       </c>
       <c r="BK33" s="22">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>5119.8</v>
       </c>
       <c r="BL33" s="22">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>5352.2</v>
       </c>
       <c r="BM33" s="22">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>5266.1</v>
       </c>
       <c r="BN33" s="22">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>5417.7</v>
       </c>
       <c r="BO33" s="22">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>5280.1</v>
       </c>
       <c r="BP33" s="22">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="BQ33" s="22">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="BR33" s="22">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="BS33" s="22"/>
@@ -6116,11 +6119,11 @@
         <v>644.84625000000005</v>
       </c>
       <c r="M34" s="18">
-        <f t="shared" ref="M34:N34" si="73">+M33-M35</f>
+        <f t="shared" ref="M34:N34" si="74">+M33-M35</f>
         <v>630.85500000000002</v>
       </c>
       <c r="N34" s="18">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>672.3275000000001</v>
       </c>
       <c r="O34" s="18"/>
@@ -6210,23 +6213,23 @@
         <v>2141</v>
       </c>
       <c r="BF34" s="18">
-        <f t="shared" ref="BF34:BJ34" si="74">+BF33-BF35</f>
+        <f t="shared" ref="BF34:BJ34" si="75">+BF33-BF35</f>
         <v>2154.5840000000003</v>
       </c>
       <c r="BG34" s="18">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>2124.2680499999997</v>
       </c>
       <c r="BH34" s="18">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>2154.6950000000002</v>
       </c>
       <c r="BI34" s="18">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>2252.2566000000002</v>
       </c>
       <c r="BJ34" s="18">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>2274.6230999999998</v>
       </c>
       <c r="BK34" s="18">
@@ -6259,7 +6262,7 @@
         <v>2385.4</v>
       </c>
       <c r="CB34" s="18">
-        <f t="shared" ref="CB34:CB45" si="75">SUM(K34:N34)</f>
+        <f t="shared" ref="CB34:CB45" si="76">SUM(K34:N34)</f>
         <v>2587.6287499999999</v>
       </c>
       <c r="CC34" s="18"/>
@@ -6302,11 +6305,11 @@
         <v>1934.5387499999997</v>
       </c>
       <c r="M35" s="18">
-        <f t="shared" ref="M35:N35" si="76">+M33*M50</f>
+        <f t="shared" ref="M35:N35" si="77">+M33*M50</f>
         <v>1892.5650000000001</v>
       </c>
       <c r="N35" s="18">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>2016.9825000000003</v>
       </c>
       <c r="O35" s="18"/>
@@ -6338,35 +6341,35 @@
       <c r="AO35" s="18"/>
       <c r="AP35" s="18"/>
       <c r="AQ35" s="18">
-        <f t="shared" ref="AQ35:AX35" si="77">AQ33-AQ34</f>
+        <f t="shared" ref="AQ35:AX35" si="78">AQ33-AQ34</f>
         <v>2405.8000000000002</v>
       </c>
       <c r="AR35" s="18">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>2560.6999999999998</v>
       </c>
       <c r="AS35" s="18">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>2619.7999999999997</v>
       </c>
       <c r="AT35" s="18">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>2747.3</v>
       </c>
       <c r="AU35" s="18">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>2772.8999999999996</v>
       </c>
       <c r="AV35" s="18">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>2566.0000000000005</v>
       </c>
       <c r="AW35" s="18">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>2719.4000000000005</v>
       </c>
       <c r="AX35" s="18">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>2851</v>
       </c>
       <c r="AY35" s="18">
@@ -6398,23 +6401,23 @@
         <v>3664.6000000000004</v>
       </c>
       <c r="BF35" s="18">
-        <f t="shared" ref="BF35:BJ35" si="78">+BF33*0.63</f>
+        <f t="shared" ref="BF35:BJ35" si="79">+BF33*0.63</f>
         <v>3668.6160000000004</v>
       </c>
       <c r="BG35" s="18">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>3616.9969499999997</v>
       </c>
       <c r="BH35" s="18">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>3668.8049999999998</v>
       </c>
       <c r="BI35" s="18">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>3834.9234000000001</v>
       </c>
       <c r="BJ35" s="18">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>3873.0069000000003</v>
       </c>
       <c r="BK35" s="18">
@@ -6422,19 +6425,19 @@
         <v>3009.2000000000003</v>
       </c>
       <c r="BL35" s="18">
-        <f t="shared" ref="BL35:BO35" si="79">+BL33-BL34</f>
+        <f t="shared" ref="BL35:BO35" si="80">+BL33-BL34</f>
         <v>3233</v>
       </c>
       <c r="BM35" s="18">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>3144.1000000000004</v>
       </c>
       <c r="BN35" s="18">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>3098.3999999999996</v>
       </c>
       <c r="BO35" s="18">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>3144.6000000000004</v>
       </c>
       <c r="BP35" s="18"/>
@@ -6586,23 +6589,23 @@
         <v>1063.5999999999999</v>
       </c>
       <c r="BF36" s="18">
-        <f t="shared" ref="BF36:BJ36" si="80">+BB36*1.05</f>
+        <f t="shared" ref="BF36:BJ36" si="81">+BB36*1.05</f>
         <v>1094.5200000000002</v>
       </c>
       <c r="BG36" s="18">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>989.5200000000001</v>
       </c>
       <c r="BH36" s="18">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>1091.895</v>
       </c>
       <c r="BI36" s="18">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>1116.78</v>
       </c>
       <c r="BJ36" s="18">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>1149.2460000000003</v>
       </c>
       <c r="BK36" s="18">
@@ -6631,11 +6634,11 @@
       <c r="BY36" s="18"/>
       <c r="BZ36" s="18"/>
       <c r="CA36" s="18">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>2234.5</v>
       </c>
       <c r="CB36" s="18">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>2457.9</v>
       </c>
       <c r="CC36" s="18"/>
@@ -6673,11 +6676,11 @@
         <v>117.3</v>
       </c>
       <c r="M37" s="18">
-        <f t="shared" ref="M37:N37" si="81">+I37</f>
+        <f t="shared" ref="M37:N37" si="82">+I37</f>
         <v>115.8</v>
       </c>
       <c r="N37" s="18">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>121.69999999999997</v>
       </c>
       <c r="O37" s="18"/>
@@ -6744,11 +6747,11 @@
       <c r="BY37" s="18"/>
       <c r="BZ37" s="18"/>
       <c r="CA37" s="18">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>477</v>
       </c>
       <c r="CB37" s="18">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>466.09999999999997</v>
       </c>
       <c r="CC37" s="18"/>
@@ -6864,23 +6867,23 @@
         <v>297</v>
       </c>
       <c r="BF38" s="18">
-        <f t="shared" ref="BF38" si="82">+BB38*1.05</f>
+        <f t="shared" ref="BF38" si="83">+BB38*1.05</f>
         <v>367.81500000000005</v>
       </c>
       <c r="BG38" s="18">
-        <f t="shared" ref="BG38" si="83">+BC38*1.05</f>
+        <f t="shared" ref="BG38" si="84">+BC38*1.05</f>
         <v>301.56</v>
       </c>
       <c r="BH38" s="18">
-        <f t="shared" ref="BH38" si="84">+BD38*1.05</f>
+        <f t="shared" ref="BH38" si="85">+BD38*1.05</f>
         <v>347.02500000000003</v>
       </c>
       <c r="BI38" s="18">
-        <f t="shared" ref="BI38" si="85">+BE38*1.05</f>
+        <f t="shared" ref="BI38" si="86">+BE38*1.05</f>
         <v>311.85000000000002</v>
       </c>
       <c r="BJ38" s="18">
-        <f t="shared" ref="BJ38" si="86">+BF38*1.05</f>
+        <f t="shared" ref="BJ38" si="87">+BF38*1.05</f>
         <v>386.20575000000008</v>
       </c>
       <c r="BK38" s="18">
@@ -6909,11 +6912,11 @@
       <c r="BY38" s="18"/>
       <c r="BZ38" s="18"/>
       <c r="CA38" s="18">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>478.20000000000005</v>
       </c>
       <c r="CB38" s="18">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>514.9</v>
       </c>
       <c r="CC38" s="18"/>
@@ -6951,11 +6954,11 @@
         <v>109.4</v>
       </c>
       <c r="M39" s="18">
-        <f t="shared" ref="M39" si="87">+I39</f>
+        <f t="shared" ref="M39" si="88">+I39</f>
         <v>91</v>
       </c>
       <c r="N39" s="18">
-        <f t="shared" ref="N39" si="88">+J39</f>
+        <f t="shared" ref="N39" si="89">+J39</f>
         <v>55.099999999999966</v>
       </c>
       <c r="O39" s="18"/>
@@ -7022,11 +7025,11 @@
       <c r="BY39" s="18"/>
       <c r="BZ39" s="18"/>
       <c r="CA39" s="18">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>390.4</v>
       </c>
       <c r="CB39" s="18">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>352.59999999999997</v>
       </c>
       <c r="CC39" s="18"/>
@@ -7142,23 +7145,23 @@
         <v>620</v>
       </c>
       <c r="BF40" s="18">
-        <f t="shared" ref="BF40" si="89">+BB40*1.05</f>
+        <f t="shared" ref="BF40" si="90">+BB40*1.05</f>
         <v>621.495</v>
       </c>
       <c r="BG40" s="18">
-        <f t="shared" ref="BG40" si="90">+BC40*1.05</f>
+        <f t="shared" ref="BG40" si="91">+BC40*1.05</f>
         <v>614.77499999999998</v>
       </c>
       <c r="BH40" s="18">
-        <f t="shared" ref="BH40" si="91">+BD40*1.05</f>
+        <f t="shared" ref="BH40" si="92">+BD40*1.05</f>
         <v>629.58000000000004</v>
       </c>
       <c r="BI40" s="18">
-        <f t="shared" ref="BI40" si="92">+BE40*1.05</f>
+        <f t="shared" ref="BI40" si="93">+BE40*1.05</f>
         <v>651</v>
       </c>
       <c r="BJ40" s="18">
-        <f t="shared" ref="BJ40" si="93">+BF40*1.05</f>
+        <f t="shared" ref="BJ40" si="94">+BF40*1.05</f>
         <v>652.56975</v>
       </c>
       <c r="BK40" s="18">
@@ -7187,11 +7190,11 @@
       <c r="BY40" s="18"/>
       <c r="BZ40" s="18"/>
       <c r="CA40" s="18">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>1397.1</v>
       </c>
       <c r="CB40" s="18">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>1519.5</v>
       </c>
       <c r="CC40" s="18"/>
@@ -7230,15 +7233,15 @@
         <v>1304.4000000000001</v>
       </c>
       <c r="L41" s="18">
-        <f t="shared" ref="L41:N41" si="94">SUM(L36:L40)</f>
+        <f t="shared" ref="L41:N41" si="95">SUM(L36:L40)</f>
         <v>1326.9</v>
       </c>
       <c r="M41" s="18">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>1315.1</v>
       </c>
       <c r="N41" s="18">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>1364.6</v>
       </c>
       <c r="O41" s="18"/>
@@ -7270,35 +7273,35 @@
       <c r="AO41" s="18"/>
       <c r="AP41" s="18"/>
       <c r="AQ41" s="18">
-        <f t="shared" ref="AQ41:AX41" si="95">SUM(AQ36:AQ40)</f>
+        <f t="shared" ref="AQ41:AX41" si="96">SUM(AQ36:AQ40)</f>
         <v>1677.7999999999997</v>
       </c>
       <c r="AR41" s="18">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>1754.2</v>
       </c>
       <c r="AS41" s="18">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>1708.6000000000001</v>
       </c>
       <c r="AT41" s="18">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>1935.4</v>
       </c>
       <c r="AU41" s="18">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>1767.6000000000001</v>
       </c>
       <c r="AV41" s="18">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>1688</v>
       </c>
       <c r="AW41" s="18">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>1644</v>
       </c>
       <c r="AX41" s="18">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>1948</v>
       </c>
       <c r="AY41" s="18">
@@ -7306,67 +7309,67 @@
         <v>1708.5</v>
       </c>
       <c r="AZ41" s="18">
-        <f t="shared" ref="AZ41:BD41" si="96">SUM(AZ36:AZ40)</f>
+        <f t="shared" ref="AZ41:BD41" si="97">SUM(AZ36:AZ40)</f>
         <v>1781.9</v>
       </c>
       <c r="BA41" s="18">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>1893</v>
       </c>
       <c r="BB41" s="18">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>1984.6</v>
       </c>
       <c r="BC41" s="18">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>1815.1000000000001</v>
       </c>
       <c r="BD41" s="18">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>1970</v>
       </c>
       <c r="BE41" s="18">
-        <f t="shared" ref="BE41" si="97">SUM(BE36:BE40)</f>
+        <f t="shared" ref="BE41" si="98">SUM(BE36:BE40)</f>
         <v>1980.6</v>
       </c>
       <c r="BF41" s="18">
-        <f t="shared" ref="BF41" si="98">SUM(BF36:BF40)</f>
+        <f t="shared" ref="BF41" si="99">SUM(BF36:BF40)</f>
         <v>2083.8300000000004</v>
       </c>
       <c r="BG41" s="18">
-        <f t="shared" ref="BG41" si="99">SUM(BG36:BG40)</f>
+        <f t="shared" ref="BG41" si="100">SUM(BG36:BG40)</f>
         <v>1905.855</v>
       </c>
       <c r="BH41" s="18">
-        <f t="shared" ref="BH41" si="100">SUM(BH36:BH40)</f>
+        <f t="shared" ref="BH41" si="101">SUM(BH36:BH40)</f>
         <v>2068.5</v>
       </c>
       <c r="BI41" s="18">
-        <f t="shared" ref="BI41" si="101">SUM(BI36:BI40)</f>
+        <f t="shared" ref="BI41" si="102">SUM(BI36:BI40)</f>
         <v>2079.63</v>
       </c>
       <c r="BJ41" s="18">
-        <f t="shared" ref="BJ41:BO41" si="102">SUM(BJ36:BJ40)</f>
+        <f t="shared" ref="BJ41:BO41" si="103">SUM(BJ36:BJ40)</f>
         <v>2188.0215000000003</v>
       </c>
       <c r="BK41" s="18">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>1999.4</v>
       </c>
       <c r="BL41" s="18">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>2129.4</v>
       </c>
       <c r="BM41" s="18">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>1933.6000000000001</v>
       </c>
       <c r="BN41" s="18">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>2122.6999999999998</v>
       </c>
       <c r="BO41" s="18">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>2018.6</v>
       </c>
       <c r="BP41" s="18"/>
@@ -7403,35 +7406,35 @@
       </c>
       <c r="F42" s="18"/>
       <c r="G42" s="18">
-        <f t="shared" ref="G42:N42" si="103">G35-G41</f>
+        <f t="shared" ref="G42:N42" si="104">G35-G41</f>
         <v>435.40000000000032</v>
       </c>
       <c r="H42" s="18">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>469.89999999999986</v>
       </c>
       <c r="I42" s="18">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>561.49999999999977</v>
       </c>
       <c r="J42" s="18">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>461.20000000000073</v>
       </c>
       <c r="K42" s="18">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>619.69999999999982</v>
       </c>
       <c r="L42" s="18">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>607.63874999999962</v>
       </c>
       <c r="M42" s="18">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>577.46500000000015</v>
       </c>
       <c r="N42" s="18">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>652.38250000000039</v>
       </c>
       <c r="O42" s="18"/>
@@ -7463,35 +7466,35 @@
       <c r="AO42" s="18"/>
       <c r="AP42" s="18"/>
       <c r="AQ42" s="18">
-        <f t="shared" ref="AQ42:AX42" si="104">AQ35-AQ41</f>
+        <f t="shared" ref="AQ42:AX42" si="105">AQ35-AQ41</f>
         <v>728.00000000000045</v>
       </c>
       <c r="AR42" s="18">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>806.49999999999977</v>
       </c>
       <c r="AS42" s="18">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>911.19999999999959</v>
       </c>
       <c r="AT42" s="18">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>811.90000000000009</v>
       </c>
       <c r="AU42" s="18">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>1005.2999999999995</v>
       </c>
       <c r="AV42" s="18">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>878.00000000000045</v>
       </c>
       <c r="AW42" s="18">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>1075.4000000000005</v>
       </c>
       <c r="AX42" s="18">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>903</v>
       </c>
       <c r="AY42" s="18">
@@ -7499,67 +7502,67 @@
         <v>1254.8000000000002</v>
       </c>
       <c r="AZ42" s="18">
-        <f t="shared" ref="AZ42:BD42" si="105">AZ35-AZ41</f>
+        <f t="shared" ref="AZ42:BD42" si="106">AZ35-AZ41</f>
         <v>1325.1</v>
       </c>
       <c r="BA42" s="18">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>1270.1000000000004</v>
       </c>
       <c r="BB42" s="18">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>1270.5999999999999</v>
       </c>
       <c r="BC42" s="18">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>1446.5000000000002</v>
       </c>
       <c r="BD42" s="18">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>1543.6</v>
       </c>
       <c r="BE42" s="18">
-        <f t="shared" ref="BE42" si="106">BE35-BE41</f>
+        <f t="shared" ref="BE42" si="107">BE35-BE41</f>
         <v>1684.0000000000005</v>
       </c>
       <c r="BF42" s="18">
-        <f t="shared" ref="BF42" si="107">BF35-BF41</f>
+        <f t="shared" ref="BF42" si="108">BF35-BF41</f>
         <v>1584.7860000000001</v>
       </c>
       <c r="BG42" s="18">
-        <f t="shared" ref="BG42" si="108">BG35-BG41</f>
+        <f t="shared" ref="BG42" si="109">BG35-BG41</f>
         <v>1711.1419499999997</v>
       </c>
       <c r="BH42" s="18">
-        <f t="shared" ref="BH42" si="109">BH35-BH41</f>
+        <f t="shared" ref="BH42" si="110">BH35-BH41</f>
         <v>1600.3049999999998</v>
       </c>
       <c r="BI42" s="18">
-        <f t="shared" ref="BI42" si="110">BI35-BI41</f>
+        <f t="shared" ref="BI42" si="111">BI35-BI41</f>
         <v>1755.2934</v>
       </c>
       <c r="BJ42" s="18">
-        <f t="shared" ref="BJ42:BO42" si="111">BJ35-BJ41</f>
+        <f t="shared" ref="BJ42:BO42" si="112">BJ35-BJ41</f>
         <v>1684.9854</v>
       </c>
       <c r="BK42" s="18">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>1009.8000000000002</v>
       </c>
       <c r="BL42" s="18">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>1103.5999999999999</v>
       </c>
       <c r="BM42" s="18">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>1210.5000000000002</v>
       </c>
       <c r="BN42" s="18">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>975.69999999999982</v>
       </c>
       <c r="BO42" s="18">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>1126.0000000000005</v>
       </c>
       <c r="BP42" s="18"/>
@@ -7693,23 +7696,23 @@
         <v>-47</v>
       </c>
       <c r="BF43" s="18">
-        <f t="shared" ref="BF43:BJ43" si="112">AVERAGE(BB43:BE43)</f>
+        <f t="shared" ref="BF43:BJ43" si="113">AVERAGE(BB43:BE43)</f>
         <v>-45.8</v>
       </c>
       <c r="BG43" s="18">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>-45.55</v>
       </c>
       <c r="BH43" s="18">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>-48.362499999999997</v>
       </c>
       <c r="BI43" s="18">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>-46.678124999999994</v>
       </c>
       <c r="BJ43" s="18">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>-46.597656249999993</v>
       </c>
       <c r="BK43" s="18">
@@ -7738,11 +7741,11 @@
       <c r="BY43" s="18"/>
       <c r="BZ43" s="18"/>
       <c r="CA43" s="18">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>251.6</v>
       </c>
       <c r="CB43" s="18">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>271.3</v>
       </c>
       <c r="CC43" s="18"/>
@@ -7761,35 +7764,35 @@
       </c>
       <c r="F44" s="18"/>
       <c r="G44" s="18">
-        <f t="shared" ref="G44:N44" si="113">+G42-G43</f>
+        <f t="shared" ref="G44:N44" si="114">+G42-G43</f>
         <v>396.8000000000003</v>
       </c>
       <c r="H44" s="18">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>391.59999999999985</v>
       </c>
       <c r="I44" s="18">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>487.29999999999978</v>
       </c>
       <c r="J44" s="18">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>400.70000000000073</v>
       </c>
       <c r="K44" s="18">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>551.39999999999986</v>
       </c>
       <c r="L44" s="18">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>539.63874999999962</v>
       </c>
       <c r="M44" s="18">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>509.46500000000015</v>
       </c>
       <c r="N44" s="18">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>585.38250000000039</v>
       </c>
       <c r="O44" s="18"/>
@@ -7821,35 +7824,35 @@
       <c r="AO44" s="18"/>
       <c r="AP44" s="18"/>
       <c r="AQ44" s="18">
-        <f t="shared" ref="AQ44:AX44" si="114">AQ42+AQ43</f>
+        <f t="shared" ref="AQ44:AX44" si="115">AQ42+AQ43</f>
         <v>615.40000000000043</v>
       </c>
       <c r="AR44" s="18">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>745.39999999999975</v>
       </c>
       <c r="AS44" s="18">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>776.29999999999961</v>
       </c>
       <c r="AT44" s="18">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>735.80000000000007</v>
       </c>
       <c r="AU44" s="18">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>906.7999999999995</v>
       </c>
       <c r="AV44" s="18">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>775.7000000000005</v>
       </c>
       <c r="AW44" s="18">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>973.80000000000052</v>
       </c>
       <c r="AX44" s="18">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>851</v>
       </c>
       <c r="AY44" s="18">
@@ -7857,67 +7860,67 @@
         <v>1195.7000000000003</v>
       </c>
       <c r="AZ44" s="18">
-        <f t="shared" ref="AZ44:BD44" si="115">AZ42+AZ43</f>
+        <f t="shared" ref="AZ44:BD44" si="116">AZ42+AZ43</f>
         <v>1230.3</v>
       </c>
       <c r="BA44" s="18">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>1215.9000000000003</v>
       </c>
       <c r="BB44" s="18">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>1223.8</v>
       </c>
       <c r="BC44" s="18">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>1412.2000000000003</v>
       </c>
       <c r="BD44" s="18">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>1488.5</v>
       </c>
       <c r="BE44" s="18">
-        <f t="shared" ref="BE44" si="116">BE42+BE43</f>
+        <f t="shared" ref="BE44" si="117">BE42+BE43</f>
         <v>1637.0000000000005</v>
       </c>
       <c r="BF44" s="18">
-        <f t="shared" ref="BF44" si="117">BF42+BF43</f>
+        <f t="shared" ref="BF44" si="118">BF42+BF43</f>
         <v>1538.9860000000001</v>
       </c>
       <c r="BG44" s="18">
-        <f t="shared" ref="BG44" si="118">BG42+BG43</f>
+        <f t="shared" ref="BG44" si="119">BG42+BG43</f>
         <v>1665.5919499999998</v>
       </c>
       <c r="BH44" s="18">
-        <f t="shared" ref="BH44" si="119">BH42+BH43</f>
+        <f t="shared" ref="BH44" si="120">BH42+BH43</f>
         <v>1551.9424999999999</v>
       </c>
       <c r="BI44" s="18">
-        <f t="shared" ref="BI44" si="120">BI42+BI43</f>
+        <f t="shared" ref="BI44" si="121">BI42+BI43</f>
         <v>1708.6152750000001</v>
       </c>
       <c r="BJ44" s="18">
-        <f t="shared" ref="BJ44:BO44" si="121">BJ42+BJ43</f>
+        <f t="shared" ref="BJ44:BO44" si="122">BJ42+BJ43</f>
         <v>1638.38774375</v>
       </c>
       <c r="BK44" s="18">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>977.60000000000014</v>
       </c>
       <c r="BL44" s="18">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>1096.3999999999999</v>
       </c>
       <c r="BM44" s="18">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>1156.4000000000003</v>
       </c>
       <c r="BN44" s="18">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>960.69999999999982</v>
       </c>
       <c r="BO44" s="18">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>1076.2000000000005</v>
       </c>
       <c r="BP44" s="18"/>
@@ -8057,23 +8060,23 @@
         <v>264</v>
       </c>
       <c r="BF45" s="18">
-        <f t="shared" ref="BF45:BJ45" si="122">+BF44*0.15</f>
+        <f t="shared" ref="BF45:BJ45" si="123">+BF44*0.15</f>
         <v>230.84790000000001</v>
       </c>
       <c r="BG45" s="18">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>249.83879249999995</v>
       </c>
       <c r="BH45" s="18">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>232.79137499999996</v>
       </c>
       <c r="BI45" s="18">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>256.29229125000001</v>
       </c>
       <c r="BJ45" s="18">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>245.75816156249999</v>
       </c>
       <c r="BK45" s="18">
@@ -8102,11 +8105,11 @@
       <c r="BY45" s="18"/>
       <c r="BZ45" s="18"/>
       <c r="CA45" s="18">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>219.60000000000002</v>
       </c>
       <c r="CB45" s="18">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>480.4</v>
       </c>
       <c r="CC45" s="18"/>
@@ -8125,35 +8128,35 @@
       </c>
       <c r="F46" s="18"/>
       <c r="G46" s="18">
-        <f t="shared" ref="G46:N46" si="123">+G44-G45</f>
+        <f t="shared" ref="G46:N46" si="124">+G44-G45</f>
         <v>332.20000000000027</v>
       </c>
       <c r="H46" s="18">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>331.69999999999987</v>
       </c>
       <c r="I46" s="18">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>412.49999999999977</v>
       </c>
       <c r="J46" s="18">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>380.40000000000072</v>
       </c>
       <c r="K46" s="18">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>431.29999999999984</v>
       </c>
       <c r="L46" s="18">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>419.5387499999996</v>
       </c>
       <c r="M46" s="18">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>389.36500000000012</v>
       </c>
       <c r="N46" s="18">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>465.28250000000037</v>
       </c>
       <c r="O46" s="18"/>
@@ -8185,35 +8188,35 @@
       <c r="AO46" s="18"/>
       <c r="AP46" s="18"/>
       <c r="AQ46" s="18">
-        <f t="shared" ref="AQ46:AX46" si="124">AQ44-AQ45</f>
+        <f t="shared" ref="AQ46:AX46" si="125">AQ44-AQ45</f>
         <v>548.20000000000039</v>
       </c>
       <c r="AR46" s="18">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>609.19999999999982</v>
       </c>
       <c r="AS46" s="18">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>642.59999999999968</v>
       </c>
       <c r="AT46" s="18">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>633.20000000000005</v>
       </c>
       <c r="AU46" s="18">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>747.39999999999952</v>
       </c>
       <c r="AV46" s="18">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>675.80000000000052</v>
       </c>
       <c r="AW46" s="18">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>715.30000000000052</v>
       </c>
       <c r="AX46" s="18">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>732.2</v>
       </c>
       <c r="AY46" s="18">
@@ -8221,67 +8224,67 @@
         <v>959.50000000000023</v>
       </c>
       <c r="AZ46" s="18">
-        <f t="shared" ref="AZ46:BD46" si="125">AZ44-AZ45</f>
+        <f t="shared" ref="AZ46:BD46" si="126">AZ44-AZ45</f>
         <v>1022.5</v>
       </c>
       <c r="BA46" s="18">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>986.50000000000034</v>
       </c>
       <c r="BB46" s="18">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>1038.3999999999999</v>
       </c>
       <c r="BC46" s="18">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>1156.8000000000002</v>
       </c>
       <c r="BD46" s="18">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>1236.8</v>
       </c>
       <c r="BE46" s="18">
-        <f t="shared" ref="BE46" si="126">BE44-BE45</f>
+        <f t="shared" ref="BE46" si="127">BE44-BE45</f>
         <v>1373.0000000000005</v>
       </c>
       <c r="BF46" s="18">
-        <f t="shared" ref="BF46" si="127">BF44-BF45</f>
+        <f t="shared" ref="BF46" si="128">BF44-BF45</f>
         <v>1308.1381000000001</v>
       </c>
       <c r="BG46" s="18">
-        <f t="shared" ref="BG46" si="128">BG44-BG45</f>
+        <f t="shared" ref="BG46" si="129">BG44-BG45</f>
         <v>1415.7531574999998</v>
       </c>
       <c r="BH46" s="18">
-        <f t="shared" ref="BH46" si="129">BH44-BH45</f>
+        <f t="shared" ref="BH46" si="130">BH44-BH45</f>
         <v>1319.1511249999999</v>
       </c>
       <c r="BI46" s="18">
-        <f t="shared" ref="BI46" si="130">BI44-BI45</f>
+        <f t="shared" ref="BI46" si="131">BI44-BI45</f>
         <v>1452.32298375</v>
       </c>
       <c r="BJ46" s="18">
-        <f t="shared" ref="BJ46:BO46" si="131">BJ44-BJ45</f>
+        <f t="shared" ref="BJ46:BO46" si="132">BJ44-BJ45</f>
         <v>1392.6295821875001</v>
       </c>
       <c r="BK46" s="18">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>778.00000000000011</v>
       </c>
       <c r="BL46" s="18">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>916.59999999999991</v>
       </c>
       <c r="BM46" s="18">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>925.10000000000036</v>
       </c>
       <c r="BN46" s="18">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>820.79999999999984</v>
       </c>
       <c r="BO46" s="18">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>858.30000000000052</v>
       </c>
       <c r="BP46" s="18"/>
@@ -8351,35 +8354,35 @@
       <c r="AO47" s="18"/>
       <c r="AP47" s="18"/>
       <c r="AQ47" s="31">
-        <f t="shared" ref="AQ47:AX47" si="132">+AQ46/AQ48</f>
+        <f t="shared" ref="AQ47:AX47" si="133">+AQ46/AQ48</f>
         <v>1.2608095676172961</v>
       </c>
       <c r="AR47" s="31">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>1.4011039558417659</v>
       </c>
       <c r="AS47" s="31">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>1.4779208831646726</v>
       </c>
       <c r="AT47" s="31">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>1.4563017479300828</v>
       </c>
       <c r="AU47" s="31">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>1.7189512419503208</v>
       </c>
       <c r="AV47" s="31">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>1.5542778288868457</v>
       </c>
       <c r="AW47" s="31">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>1.6451241950322</v>
       </c>
       <c r="AX47" s="31">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>1.6839926402943883</v>
       </c>
       <c r="AY47" s="31">
@@ -8387,67 +8390,67 @@
         <v>2.2067617295308191</v>
       </c>
       <c r="AZ47" s="31">
-        <f t="shared" ref="AZ47:BO47" si="133">+AZ46/AZ48</f>
+        <f t="shared" ref="AZ47:BO47" si="134">+AZ46/AZ48</f>
         <v>2.3516559337626495</v>
       </c>
       <c r="BA47" s="31">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>2.2688592456301757</v>
       </c>
       <c r="BB47" s="31">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>2.3882244710211586</v>
       </c>
       <c r="BC47" s="31">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>2.660533578656854</v>
       </c>
       <c r="BD47" s="31">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>2.8445262189512417</v>
       </c>
       <c r="BE47" s="31">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>3.1577736890524388</v>
       </c>
       <c r="BF47" s="31">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>3.0085972861085559</v>
       </c>
       <c r="BG47" s="31">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>3.2561020181692726</v>
       </c>
       <c r="BH47" s="31">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>3.0339262304507817</v>
       </c>
       <c r="BI47" s="31">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>3.3402092542548298</v>
       </c>
       <c r="BJ47" s="31">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>3.2029199222343609</v>
       </c>
       <c r="BK47" s="31">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>1.7893284268629257</v>
       </c>
       <c r="BL47" s="31">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>2.1080956761729528</v>
       </c>
       <c r="BM47" s="31">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>2.1276448942042325</v>
       </c>
       <c r="BN47" s="31">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>1.8877644894204229</v>
       </c>
       <c r="BO47" s="31">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>1.9740110395584187</v>
       </c>
       <c r="BP47" s="31"/>
@@ -8606,7 +8609,7 @@
         <v>81</v>
       </c>
       <c r="E50" s="24">
-        <f t="shared" ref="E50" si="134">E35/E33</f>
+        <f t="shared" ref="E50" si="135">E35/E33</f>
         <v>0.73235897435897435</v>
       </c>
       <c r="G50" s="24">
@@ -8614,11 +8617,11 @@
         <v>0.76816427652579933</v>
       </c>
       <c r="H50" s="24">
-        <f t="shared" ref="H50:K50" si="135">H35/H33</f>
+        <f t="shared" ref="H50:K50" si="136">H35/H33</f>
         <v>0.76576086956521738</v>
       </c>
       <c r="I50" s="24">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>0.74580581648139788</v>
       </c>
       <c r="J50" s="24">
@@ -8626,7 +8629,7 @@
         <v>0.7007227590541284</v>
       </c>
       <c r="K50" s="24">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>0.75051683114248935</v>
       </c>
       <c r="L50" s="24">
@@ -8667,35 +8670,35 @@
       <c r="AO50" s="24"/>
       <c r="AP50" s="24"/>
       <c r="AQ50" s="24">
-        <f t="shared" ref="AQ50:AX50" si="136">AQ35/AQ33</f>
+        <f t="shared" ref="AQ50:AX50" si="137">AQ35/AQ33</f>
         <v>0.64226600459180949</v>
       </c>
       <c r="AR50" s="24">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>0.6447852142821171</v>
       </c>
       <c r="AS50" s="24">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>0.64627377457631296</v>
       </c>
       <c r="AT50" s="24">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>0.62712289992695402</v>
       </c>
       <c r="AU50" s="24">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>0.6345744559123051</v>
       </c>
       <c r="AV50" s="24">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>0.62295161564419421</v>
       </c>
       <c r="AW50" s="24">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>0.61149962897168952</v>
       </c>
       <c r="AX50" s="24">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>0.61998477764488424</v>
       </c>
       <c r="AY50" s="24">
@@ -8703,47 +8706,47 @@
         <v>0.64002159827213823</v>
       </c>
       <c r="AZ50" s="24">
-        <f t="shared" ref="AZ50:BD50" si="137">AZ35/AZ33</f>
+        <f t="shared" ref="AZ50:BD50" si="138">AZ35/AZ33</f>
         <v>0.63785670293574215</v>
       </c>
       <c r="BA50" s="24">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>0.63631060148863416</v>
       </c>
       <c r="BB50" s="24">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>0.62431914077483697</v>
       </c>
       <c r="BC50" s="24">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>0.62743589250331844</v>
       </c>
       <c r="BD50" s="24">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>0.63092117076674448</v>
       </c>
       <c r="BE50" s="24">
-        <f t="shared" ref="BE50:BJ50" si="138">BE35/BE33</f>
+        <f t="shared" ref="BE50:BJ50" si="139">BE35/BE33</f>
         <v>0.63121813421524053</v>
       </c>
       <c r="BF50" s="24">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>0.63</v>
       </c>
       <c r="BG50" s="24">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>0.63</v>
       </c>
       <c r="BH50" s="24">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>0.63</v>
       </c>
       <c r="BI50" s="24">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>0.63</v>
       </c>
       <c r="BJ50" s="24">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>0.63</v>
       </c>
       <c r="BK50" s="24"/>
@@ -8782,15 +8785,15 @@
         <v>0.22144933060174354</v>
       </c>
       <c r="L51" s="33">
-        <f t="shared" ref="L51:N51" si="139">L33/H33-1</f>
+        <f t="shared" ref="L51:N51" si="140">L33/H33-1</f>
         <v>0.16819972826086937</v>
       </c>
       <c r="M51" s="33">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>3.5079371590303277E-2</v>
       </c>
       <c r="N51" s="33">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>5.6371278183674933E-2</v>
       </c>
       <c r="O51" s="33"/>
@@ -8830,31 +8833,31 @@
         <v>0.16655988039938063</v>
       </c>
       <c r="AV51" s="33">
-        <f t="shared" ref="AV51:BB51" si="140">AV33/AR33-1</f>
+        <f t="shared" ref="AV51:BB51" si="141">AV33/AR33-1</f>
         <v>3.7190915042554229E-2</v>
       </c>
       <c r="AW51" s="33">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>9.7047142117078433E-2</v>
       </c>
       <c r="AX51" s="33">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>4.9694119795471003E-2</v>
       </c>
       <c r="AY51" s="33">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>5.956930681740169E-2</v>
       </c>
       <c r="AZ51" s="33">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>0.18253987521545967</v>
       </c>
       <c r="BA51" s="33">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>0.11780711025162449</v>
       </c>
       <c r="BB51" s="33">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>0.13384799391105795</v>
       </c>
       <c r="BC51" s="33">
@@ -8866,27 +8869,27 @@
         <v>0.1432970642578526</v>
       </c>
       <c r="BE51" s="33">
-        <f t="shared" ref="BE51:BJ51" si="141">BE33/BA33-1</f>
+        <f t="shared" ref="BE51:BJ51" si="142">BE33/BA33-1</f>
         <v>0.16789378394689214</v>
       </c>
       <c r="BF51" s="33">
-        <f t="shared" si="141"/>
+        <f t="shared" si="142"/>
         <v>0.11683927886459555</v>
       </c>
       <c r="BG51" s="33">
-        <f t="shared" si="141"/>
+        <f t="shared" si="142"/>
         <v>0.10445049343054436</v>
       </c>
       <c r="BH51" s="33">
-        <f t="shared" si="141"/>
+        <f t="shared" si="142"/>
         <v>4.5699407434009798E-2</v>
       </c>
       <c r="BI51" s="33">
-        <f t="shared" si="141"/>
+        <f t="shared" si="142"/>
         <v>4.8501446878875587E-2</v>
       </c>
       <c r="BJ51" s="33">
-        <f t="shared" si="141"/>
+        <f t="shared" si="142"/>
         <v>5.5713353482621075E-2</v>
       </c>
       <c r="BK51" s="33"/>
@@ -8932,11 +8935,11 @@
       <c r="BA52" s="24"/>
       <c r="BB52" s="24"/>
       <c r="BC52" s="24">
-        <f t="shared" ref="BC52:BI52" si="142">+BC17/AY17-1</f>
+        <f t="shared" ref="BC52:BI52" si="143">+BC17/AY17-1</f>
         <v>9.5179987797437526E-2</v>
       </c>
       <c r="BD52" s="24">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>7.6062639821029121E-2</v>
       </c>
       <c r="BE52" s="24">
@@ -8944,19 +8947,19 @@
         <v>0.16899832120872982</v>
       </c>
       <c r="BF52" s="24">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>-2.0069296375266554E-2</v>
       </c>
       <c r="BG52" s="24">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>-1.5821727019498688E-2</v>
       </c>
       <c r="BH52" s="24">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>-1.301975051975035E-2</v>
       </c>
       <c r="BI52" s="24">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>-1.3068453805648472E-2</v>
       </c>
       <c r="BJ52" s="24">
@@ -9024,7 +9027,7 @@
         <v>0.14748944157672472</v>
       </c>
       <c r="BD54" s="24">
-        <f t="shared" ref="BD54:BJ54" si="143">+BD25/AZ25-1</f>
+        <f t="shared" ref="BD54:BJ54" si="144">+BD25/AZ25-1</f>
         <v>0.18957771787960476</v>
       </c>
       <c r="BE54" s="24">
@@ -9032,23 +9035,23 @@
         <v>0.19252669039145909</v>
       </c>
       <c r="BF54" s="24">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>0.17973595976529766</v>
       </c>
       <c r="BG54" s="24">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>0.14696151801414947</v>
       </c>
       <c r="BH54" s="24">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>1.8598942598187396E-2</v>
       </c>
       <c r="BI54" s="24">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>2.219486720381969E-2</v>
       </c>
       <c r="BJ54" s="24">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>2.3519015222835948E-2</v>
       </c>
       <c r="BK54" s="24"/>
@@ -9080,7 +9083,7 @@
         <v>0.11395348837209296</v>
       </c>
       <c r="BD55" s="24">
-        <f t="shared" ref="BD55:BJ55" si="144">+BD30/AZ30-1</f>
+        <f t="shared" ref="BD55:BJ55" si="145">+BD30/AZ30-1</f>
         <v>0.16336056009334898</v>
       </c>
       <c r="BE55" s="24">
@@ -9088,23 +9091,23 @@
         <v>0.10662393162393147</v>
       </c>
       <c r="BF55" s="24">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>0.22899159663865554</v>
       </c>
       <c r="BG55" s="24">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>0.22129436325678498</v>
       </c>
       <c r="BH55" s="24">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>0.23099297893681037</v>
       </c>
       <c r="BI55" s="24">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>0.24076076462637586</v>
       </c>
       <c r="BJ55" s="24">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>0.23400000000000021</v>
       </c>
       <c r="BK55" s="24"/>
@@ -11748,6 +11751,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100764A4B226BE2F34C80DFAA3D37A3CB30" ma:contentTypeVersion="0" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="70544b0716d1f2dd0e24adda29a3d132">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1b05d82d297216baf5b26c55225140df">
     <xsd:element name="properties">
@@ -11861,12 +11870,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -11877,6 +11880,15 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E302393A-19F6-42EF-83A3-1DE9A9F04922}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8897DFF-969D-4E20-9D67-799686BA9618}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11892,15 +11904,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E302393A-19F6-42EF-83A3-1DE9A9F04922}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22C70A9A-DFCB-424D-830E-AC04B5AD6D14}">
   <ds:schemaRefs>
